--- a/engine/arcc_study/ARCC_Valuation_Model_09092026_public.xlsx
+++ b/engine/arcc_study/ARCC_Valuation_Model_09092026_public.xlsx
@@ -5002,6 +5002,34 @@
         <v/>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>Terminal useful life: the disclosed 20 years of machinery and equipment, the class the replacement-cost base actually represents (adopted), vs the longest life disclosed in the same accounting-policies note, 50 years</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20 years</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>50 years</t>
+        </is>
+      </c>
+      <c r="D23" s="10">
+        <f>DCF!$B$44</f>
+        <v/>
+      </c>
+      <c r="E23" s="21" t="n">
+        <v>82.59023265802607</v>
+      </c>
+      <c r="F23" s="8">
+        <f>E23/D23-1</f>
+        <v/>
+      </c>
+    </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>

--- a/engine/arcc_study/ARCC_Valuation_Model_09092026_public.xlsx
+++ b/engine/arcc_study/ARCC_Valuation_Model_09092026_public.xlsx
@@ -2946,19 +2946,19 @@
         <v>0.2459972623102014</v>
       </c>
       <c r="B6" s="21" t="n">
-        <v>73.15115550310519</v>
+        <v>73.60671381117582</v>
       </c>
       <c r="C6" s="21" t="n">
-        <v>72.39121804075427</v>
+        <v>73.29785867180215</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>71.43475752289696</v>
+        <v>72.86861839558692</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>70.23400500819082</v>
+        <v>72.2897309169396</v>
       </c>
       <c r="F6" s="21" t="n">
-        <v>68.72434496386767</v>
+        <v>71.52161436728838</v>
       </c>
     </row>
     <row r="7">
@@ -2966,19 +2966,19 @@
         <v>0.2609972623102014</v>
       </c>
       <c r="B7" s="21" t="n">
-        <v>71.95537665287969</v>
+        <v>72.40207167525331</v>
       </c>
       <c r="C7" s="21" t="n">
-        <v>71.20992878008629</v>
+        <v>72.09910542072078</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>70.2717049211888</v>
+        <v>71.67804939088373</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>69.09384693657252</v>
+        <v>71.11019945464105</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>67.61297130609562</v>
+        <v>70.35672844371919</v>
       </c>
     </row>
     <row r="8">
@@ -2986,19 +2986,19 @@
         <v>0.2759972623102014</v>
       </c>
       <c r="B8" s="21" t="n">
-        <v>70.79027426617279</v>
+        <v>71.22834165907251</v>
       </c>
       <c r="C8" s="21" t="n">
-        <v>70.05893254940186</v>
+        <v>70.93110845363967</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>69.13846275838848</v>
+        <v>70.51802009299568</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>67.98289345298068</v>
+        <v>69.96091561608068</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>66.5300405232932</v>
+        <v>69.22170258351841</v>
       </c>
     </row>
     <row r="9">
@@ -3006,19 +3006,19 @@
         <v>0.2909972623102015</v>
       </c>
       <c r="B9" s="21" t="n">
-        <v>69.65480186677657</v>
+        <v>70.0844691290382</v>
       </c>
       <c r="C9" s="21" t="n">
-        <v>68.93719612025457</v>
+        <v>69.79281852114245</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>68.03401447973839</v>
+        <v>69.38748873532317</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>66.90014893501545</v>
+        <v>68.84084772623035</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>65.47458331051055</v>
+        <v>68.1155185020029</v>
       </c>
     </row>
     <row r="10">
@@ -3026,19 +3026,19 @@
         <v>0.3059972623102014</v>
       </c>
       <c r="B10" s="21" t="n">
-        <v>68.54795792803237</v>
+        <v>68.96944475378865</v>
       </c>
       <c r="C10" s="21" t="n">
-        <v>67.84373064145841</v>
+        <v>68.68323144345563</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>66.95738718745619</v>
+        <v>68.28545829765993</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>65.84466051299739</v>
+        <v>67.74900842051042</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>64.44567197863307</v>
+        <v>67.03720164648978</v>
       </c>
     </row>
     <row r="12">
@@ -3081,19 +3081,19 @@
         <v>0.2459972623102014</v>
       </c>
       <c r="B14" s="21" t="n">
-        <v>79.14869700437482</v>
+        <v>82.72422240925604</v>
       </c>
       <c r="C14" s="21" t="n">
-        <v>73.43934140744406</v>
+        <v>76.58686313962079</v>
       </c>
       <c r="D14" s="21" t="n">
-        <v>68.72434496386767</v>
+        <v>71.52161436728838</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>64.76215452853266</v>
+        <v>67.26794540134033</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>61.38363607670657</v>
+        <v>63.64343740489365</v>
       </c>
     </row>
     <row r="15">
@@ -3101,19 +3101,19 @@
         <v>0.2609972623102014</v>
       </c>
       <c r="B15" s="21" t="n">
-        <v>77.83186473658633</v>
+        <v>81.33862393403163</v>
       </c>
       <c r="C15" s="21" t="n">
-        <v>72.23505994921064</v>
+        <v>75.3222092869064</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>67.61297130609562</v>
+        <v>70.35672844371919</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>63.72881719413502</v>
+        <v>66.18679702635437</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>60.41680459456074</v>
+        <v>62.63359953789389</v>
       </c>
     </row>
     <row r="16">
@@ -3121,19 +3121,19 @@
         <v>0.2759972623102014</v>
       </c>
       <c r="B16" s="21" t="n">
-        <v>76.54905633046795</v>
+        <v>79.9888789398305</v>
       </c>
       <c r="C16" s="21" t="n">
-        <v>71.06174450953958</v>
+        <v>74.09012400998922</v>
       </c>
       <c r="D16" s="21" t="n">
-        <v>66.5300405232932</v>
+        <v>69.22170258351841</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>62.72180440330386</v>
+        <v>65.13323650827186</v>
       </c>
       <c r="F16" s="21" t="n">
-        <v>59.47449319014144</v>
+        <v>61.64941554198023</v>
       </c>
     </row>
     <row r="17">
@@ -3141,19 +3141,19 @@
         <v>0.2909972623102015</v>
       </c>
       <c r="B17" s="21" t="n">
-        <v>75.29910574798446</v>
+        <v>78.67375792410559</v>
       </c>
       <c r="C17" s="21" t="n">
-        <v>69.91833685911959</v>
+        <v>72.88949359285824</v>
       </c>
       <c r="D17" s="21" t="n">
-        <v>65.47458331051055</v>
+        <v>68.1155185020029</v>
       </c>
       <c r="E17" s="21" t="n">
-        <v>61.74022147866935</v>
+        <v>64.10632558627098</v>
       </c>
       <c r="F17" s="21" t="n">
-        <v>58.55587072908333</v>
+        <v>60.69001523698913</v>
       </c>
     </row>
     <row r="18">
@@ -3161,19 +3161,19 @@
         <v>0.3059972623102014</v>
       </c>
       <c r="B18" s="21" t="n">
-        <v>74.08089719357272</v>
+        <v>77.39208437630063</v>
       </c>
       <c r="C18" s="21" t="n">
-        <v>68.80382428307459</v>
+        <v>71.71925223450857</v>
       </c>
       <c r="D18" s="21" t="n">
-        <v>64.44567197863307</v>
+        <v>67.03720164648978</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>60.78321208802295</v>
+        <v>63.1051662251753</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>57.66014163833711</v>
+        <v>59.75456568653261</v>
       </c>
     </row>
     <row r="20">
@@ -3218,19 +3218,19 @@
         </is>
       </c>
       <c r="B22" s="21" t="n">
-        <v>79.15643371094544</v>
+        <v>82.73325110321387</v>
       </c>
       <c r="C22" s="21" t="n">
-        <v>70.34565986790007</v>
+        <v>73.29867470501917</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>63.47470890863362</v>
+        <v>65.9530942728841</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>59.23540560020016</v>
+        <v>61.42761028482793</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>55.5930443411386</v>
+        <v>57.54432734271126</v>
       </c>
     </row>
     <row r="24">
@@ -3275,19 +3275,19 @@
         </is>
       </c>
       <c r="B26" s="21" t="n">
-        <v>56.68320592500003</v>
+        <v>59.37486798522524</v>
       </c>
       <c r="C26" s="21" t="n">
-        <v>61.60662322414661</v>
+        <v>64.29828528437181</v>
       </c>
       <c r="D26" s="21" t="n">
-        <v>66.5300405232932</v>
+        <v>69.22170258351841</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>71.45345782243979</v>
+        <v>74.145119882665</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>76.37687512158635</v>
+        <v>79.06853718181156</v>
       </c>
     </row>
     <row r="28">
@@ -3332,19 +3332,19 @@
         </is>
       </c>
       <c r="B30" s="21" t="n">
-        <v>62.52862610332402</v>
+        <v>65.22028816354924</v>
       </c>
       <c r="C30" s="21" t="n">
-        <v>64.52933331330861</v>
+        <v>67.22099537353382</v>
       </c>
       <c r="D30" s="21" t="n">
-        <v>66.5300405232932</v>
+        <v>69.22170258351841</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>68.53074773327778</v>
+        <v>71.22240979350299</v>
       </c>
       <c r="F30" s="21" t="n">
-        <v>70.53145494326236</v>
+        <v>73.22311700348757</v>
       </c>
     </row>
     <row r="32">
@@ -4939,7 +4939,7 @@
         <v/>
       </c>
       <c r="E20" s="21" t="n">
-        <v>66.64442256173977</v>
+        <v>69.34158478024187</v>
       </c>
       <c r="F20" s="8">
         <f>E20/D20-1</f>
@@ -4967,7 +4967,7 @@
         <v/>
       </c>
       <c r="E21" s="21" t="n">
-        <v>74.54390340298886</v>
+        <v>77.79230702163801</v>
       </c>
       <c r="F21" s="8">
         <f>E21/D21-1</f>
@@ -4995,7 +4995,7 @@
         <v/>
       </c>
       <c r="E22" s="21" t="n">
-        <v>70.62433473497708</v>
+        <v>73.31599679520228</v>
       </c>
       <c r="F22" s="8">
         <f>E22/D22-1</f>
@@ -5023,7 +5023,7 @@
         <v/>
       </c>
       <c r="E23" s="21" t="n">
-        <v>82.59023265802607</v>
+        <v>83.62546234561067</v>
       </c>
       <c r="F23" s="8">
         <f>E23/D23-1</f>
@@ -6016,7 +6016,7 @@
         </is>
       </c>
       <c r="B38" s="24" t="n">
-        <v>0.12</v>
+        <v>0.1228457576508227</v>
       </c>
     </row>
     <row r="39">
@@ -10278,7 +10278,7 @@
         </is>
       </c>
       <c r="B22" s="17">
-        <f>Assumptions!$B$14*Assumptions!$B$153*Assumptions!$B$12*Assumptions!$G$30</f>
+        <f>Assumptions!$B$14*Assumptions!$B$153*Assumptions!$B$12*Assumptions!$G$30/Assumptions!$C$30</f>
         <v/>
       </c>
       <c r="C22" t="inlineStr">
@@ -10327,7 +10327,7 @@
         </is>
       </c>
       <c r="D24" s="17">
-        <f>Assumptions!$B$51*F5*0.12000000</f>
+        <f>Assumptions!$B$51*F5*0.12284576</f>
         <v/>
       </c>
     </row>
